--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.08088235294117647</v>
+        <v>0.07352941176470588</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.09859154929577464</v>
+        <v>0.09154929577464789</v>
       </c>
       <c r="D2">
-        <v>0.920863309352518</v>
+        <v>0.9280575539568345</v>
       </c>
       <c r="E2">
         <v>136</v>
